--- a/Data/EC/NIT-9008481153.xlsx
+++ b/Data/EC/NIT-9008481153.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7382B09C-09EC-4DBD-8B2A-FDEAF7C4CB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4DFEFF7-547C-485F-89F7-7A6EB6868770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AD0290E7-2050-46E0-83F8-554F06A00440}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8B2DD248-3997-41FF-9D3A-41F81A8B1F02}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="96">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -272,10 +272,28 @@
     <t>ALMA YANETH CASTRO MIRANDA</t>
   </si>
   <si>
+    <t>32909395</t>
+  </si>
+  <si>
+    <t>RUBY LILIANA MORENO GUARDO</t>
+  </si>
+  <si>
     <t>92028868</t>
   </si>
   <si>
     <t>EZEQUIEL ARTURO ESCOBAR ESCOBAR</t>
+  </si>
+  <si>
+    <t>1042576025</t>
+  </si>
+  <si>
+    <t>VALENTIN PADILLA DE HOYOS</t>
+  </si>
+  <si>
+    <t>1047386091</t>
+  </si>
+  <si>
+    <t>WILMER GONZALEZ QUINTERO</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -674,22 +692,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{963EB5BE-58A1-F43A-C3FC-3086B7F6E1CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78851206-5763-8B6E-BCF3-01E3884C4080}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -698,7 +716,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -711,7 +729,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1040,27 +1058,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A96490-8E5E-455E-BB5F-29EA86721787}">
-  <dimension ref="B2:J131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64DF46E-35B5-4A37-A470-8B3E0BAA2B1D}">
+  <dimension ref="B2:J143"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1069,7 +1087,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1080,7 +1098,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1091,7 +1109,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1102,10 +1120,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1118,8 +1136,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1134,15 +1152,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2921999</v>
+        <v>2947199</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1150,17 +1168,17 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C13" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F13" s="5">
         <v>62</v>
@@ -1170,7 +1188,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1190,16 +1208,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1222,7 +1240,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1245,7 +1263,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1268,7 +1286,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1291,7 +1309,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1314,7 +1332,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1337,7 +1355,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1360,7 +1378,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1383,7 +1401,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1406,7 +1424,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1429,7 +1447,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1452,7 +1470,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1475,7 +1493,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1498,7 +1516,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1521,7 +1539,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1544,7 +1562,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1567,7 +1585,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1590,7 +1608,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1613,7 +1631,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1636,7 +1654,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1659,7 +1677,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1682,7 +1700,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1705,7 +1723,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1728,7 +1746,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1751,7 +1769,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1774,7 +1792,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1797,7 +1815,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1820,7 +1838,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1843,7 +1861,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1866,7 +1884,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1889,7 +1907,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1912,7 +1930,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1935,7 +1953,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1958,7 +1976,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1981,7 +1999,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2004,7 +2022,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2027,7 +2045,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2050,7 +2068,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2073,7 +2091,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2096,7 +2114,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2137,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2142,7 +2160,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2165,7 +2183,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2188,7 +2206,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2211,7 +2229,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2234,7 +2252,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2257,7 +2275,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2280,7 +2298,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2303,7 +2321,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2326,7 +2344,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2349,7 +2367,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2372,7 +2390,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2395,7 +2413,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2418,7 +2436,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2441,7 +2459,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2464,7 +2482,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2487,7 +2505,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2510,7 +2528,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2533,7 +2551,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2556,7 +2574,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2579,7 +2597,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2602,7 +2620,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2625,7 +2643,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2666,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2671,7 +2689,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2694,7 +2712,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2717,7 +2735,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2740,7 +2758,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2763,7 +2781,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2786,7 +2804,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2809,7 +2827,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2832,7 +2850,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2855,7 +2873,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2878,7 +2896,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2901,7 +2919,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2924,7 +2942,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2947,7 +2965,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2970,7 +2988,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2993,7 +3011,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3016,7 +3034,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3039,7 +3057,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3062,7 +3080,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3085,7 +3103,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3108,7 +3126,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3131,7 +3149,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3154,7 +3172,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3177,7 +3195,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3200,7 +3218,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3223,7 +3241,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3246,7 +3264,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3269,7 +3287,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3292,7 +3310,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3315,7 +3333,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3338,7 +3356,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3361,7 +3379,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3372,19 +3390,19 @@
         <v>78</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="F110" s="18">
-        <v>28708</v>
+        <v>2100</v>
       </c>
       <c r="G110" s="18">
-        <v>828116</v>
+        <v>0</v>
       </c>
       <c r="H110" s="19"/>
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3395,19 +3413,19 @@
         <v>78</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F111" s="18">
-        <v>33125</v>
+        <v>2100</v>
       </c>
       <c r="G111" s="18">
-        <v>828116</v>
+        <v>0</v>
       </c>
       <c r="H111" s="19"/>
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3418,19 +3436,19 @@
         <v>78</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F112" s="18">
-        <v>33125</v>
+        <v>2100</v>
       </c>
       <c r="G112" s="18">
-        <v>828116</v>
+        <v>0</v>
       </c>
       <c r="H112" s="19"/>
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3441,33 +3459,33 @@
         <v>78</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F113" s="18">
-        <v>33125</v>
+        <v>2100</v>
       </c>
       <c r="G113" s="18">
-        <v>828116</v>
+        <v>0</v>
       </c>
       <c r="H113" s="19"/>
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F114" s="18">
-        <v>33125</v>
+        <v>28708</v>
       </c>
       <c r="G114" s="18">
         <v>828116</v>
@@ -3476,18 +3494,18 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F115" s="18">
         <v>33125</v>
@@ -3499,18 +3517,18 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F116" s="18">
         <v>33125</v>
@@ -3522,18 +3540,18 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F117" s="18">
         <v>33125</v>
@@ -3545,18 +3563,18 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F118" s="18">
         <v>33125</v>
@@ -3568,18 +3586,18 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F119" s="18">
         <v>33125</v>
@@ -3591,18 +3609,18 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F120" s="18">
         <v>33125</v>
@@ -3614,18 +3632,18 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F121" s="18">
         <v>33125</v>
@@ -3637,18 +3655,18 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F122" s="18">
         <v>33125</v>
@@ -3660,18 +3678,18 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F123" s="18">
         <v>33125</v>
@@ -3683,18 +3701,18 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F124" s="18">
         <v>33125</v>
@@ -3706,57 +3724,333 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B125" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D125" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E125" s="22" t="s">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B125" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D125" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F125" s="18">
+        <v>33125</v>
+      </c>
+      <c r="G125" s="18">
+        <v>828116</v>
+      </c>
+      <c r="H125" s="19"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="20"/>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B126" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F126" s="18">
+        <v>33125</v>
+      </c>
+      <c r="G126" s="18">
+        <v>828116</v>
+      </c>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="20"/>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B127" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="18">
+        <v>33125</v>
+      </c>
+      <c r="G127" s="18">
+        <v>828116</v>
+      </c>
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="20"/>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B128" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" s="18">
+        <v>33125</v>
+      </c>
+      <c r="G128" s="18">
+        <v>828116</v>
+      </c>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="20"/>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B129" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E129" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F125" s="24">
-        <v>33125</v>
-      </c>
-      <c r="G125" s="24">
-        <v>828116</v>
-      </c>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-      <c r="J125" s="26"/>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B130" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C130" s="32"/>
-      <c r="H130" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B131" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C131" s="32"/>
-      <c r="H131" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
+      <c r="F129" s="18">
+        <v>33125</v>
+      </c>
+      <c r="G129" s="18">
+        <v>828116</v>
+      </c>
+      <c r="H129" s="19"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="20"/>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B130" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F130" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G130" s="18">
+        <v>0</v>
+      </c>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="20"/>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B131" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F131" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G131" s="18">
+        <v>0</v>
+      </c>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="20"/>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B132" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E132" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F132" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G132" s="18">
+        <v>0</v>
+      </c>
+      <c r="H132" s="19"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="20"/>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B133" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E133" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F133" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G133" s="18">
+        <v>0</v>
+      </c>
+      <c r="H133" s="19"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="20"/>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B134" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E134" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F134" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G134" s="18">
+        <v>0</v>
+      </c>
+      <c r="H134" s="19"/>
+      <c r="I134" s="19"/>
+      <c r="J134" s="20"/>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B135" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E135" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F135" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G135" s="18">
+        <v>0</v>
+      </c>
+      <c r="H135" s="19"/>
+      <c r="I135" s="19"/>
+      <c r="J135" s="20"/>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B136" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E136" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F136" s="18">
+        <v>2100</v>
+      </c>
+      <c r="G136" s="18">
+        <v>0</v>
+      </c>
+      <c r="H136" s="19"/>
+      <c r="I136" s="19"/>
+      <c r="J136" s="20"/>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B137" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D137" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E137" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F137" s="24">
+        <v>2100</v>
+      </c>
+      <c r="G137" s="24">
+        <v>0</v>
+      </c>
+      <c r="H137" s="25"/>
+      <c r="I137" s="25"/>
+      <c r="J137" s="26"/>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B142" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C142" s="32"/>
+      <c r="H142" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+    </row>
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B143" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C143" s="32"/>
+      <c r="H143" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I143" s="1"/>
+      <c r="J143" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="H130:J130"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="H143:J143"/>
+    <mergeCell ref="H142:J142"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
